--- a/data/aa2_1_e.xlsx
+++ b/data/aa2_1_e.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GinrutPrices\Output\A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\odelyas\Desktop\AA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="796">
-  <si>
-    <t>Last produced for Price Statistics Monthly No. 4/2026, Central Bureau of Statistics</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="802">
+  <si>
+    <t>Last produced for Price Statistics Monthly No. 7/2026, Central Bureau of Statistics</t>
   </si>
   <si>
     <t>Base: Average 1993=100.0</t>
@@ -1207,6 +1207,24 @@
   </si>
   <si>
     <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>March 2026 - April 2026</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>April 2026 - May 2026</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>May 2026 - June 2026</t>
+  </si>
+  <si>
+    <t>15/08/2026</t>
   </si>
   <si>
     <t>(1) As of January 1999 this index serves as an indicator to changes</t>
@@ -2940,7 +2958,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -2949,7 +2967,7 @@
     </row>
     <row r="3" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2976,10 +2994,10 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -2987,10 +3005,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C7" s="11">
         <v>117.2</v>
@@ -3002,10 +3020,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C8" s="11">
         <v>119.6</v>
@@ -3017,10 +3035,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C9" s="11">
         <v>122.1</v>
@@ -3032,10 +3050,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C10" s="11">
         <v>124.3</v>
@@ -3047,10 +3065,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C11" s="11">
         <v>127.1</v>
@@ -3062,10 +3080,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C12" s="11">
         <v>129.30000000000001</v>
@@ -3077,10 +3095,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C13" s="11">
         <v>131.19999999999999</v>
@@ -3092,10 +3110,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C14" s="11">
         <v>132.5</v>
@@ -3107,10 +3125,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C15" s="11">
         <v>133.5</v>
@@ -3122,10 +3140,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C16" s="11">
         <v>135.30000000000001</v>
@@ -3137,10 +3155,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C17" s="11">
         <v>136.9</v>
@@ -3152,10 +3170,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C18" s="11">
         <v>138.9</v>
@@ -3167,10 +3185,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C19" s="11">
         <v>140.30000000000001</v>
@@ -3184,10 +3202,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C20" s="11">
         <v>140.69999999999999</v>
@@ -3201,10 +3219,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C21" s="11">
         <v>141.5</v>
@@ -3218,10 +3236,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C22" s="11">
         <v>142.69999999999999</v>
@@ -3235,10 +3253,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C23" s="11">
         <v>144.4</v>
@@ -3252,10 +3270,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C24" s="11">
         <v>145.5</v>
@@ -3269,10 +3287,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C25" s="11">
         <v>148.69999999999999</v>
@@ -3286,10 +3304,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C26" s="11">
         <v>151.80000000000001</v>
@@ -3303,10 +3321,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C27" s="11">
         <v>151.9</v>
@@ -3320,10 +3338,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C28" s="11">
         <v>153.5</v>
@@ -3337,10 +3355,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C29" s="11">
         <v>157.9</v>
@@ -3354,10 +3372,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C30" s="11">
         <v>162.69999999999999</v>
@@ -3371,10 +3389,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C31" s="11">
         <v>164.7</v>
@@ -3388,10 +3406,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C32" s="11">
         <v>164.7</v>
@@ -3405,10 +3423,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C33" s="11">
         <v>167</v>
@@ -3422,10 +3440,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C34" s="11">
         <v>171.8</v>
@@ -3439,10 +3457,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C35" s="11">
         <v>175.3</v>
@@ -3456,10 +3474,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C36" s="11">
         <v>174.6</v>
@@ -3473,10 +3491,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C37" s="11">
         <v>171.6</v>
@@ -3490,10 +3508,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C38" s="11">
         <v>170.8</v>
@@ -3507,10 +3525,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="C39" s="11">
         <v>173.5</v>
@@ -3524,10 +3542,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C40" s="11">
         <v>176.4</v>
@@ -3541,10 +3559,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C41" s="11">
         <v>177.1</v>
@@ -3558,10 +3576,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C42" s="11">
         <v>178.4</v>
@@ -3575,10 +3593,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C43" s="11">
         <v>181.8</v>
@@ -3592,10 +3610,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C44" s="11">
         <v>183</v>
@@ -3609,10 +3627,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C45" s="11">
         <v>183.2</v>
@@ -3626,10 +3644,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C46" s="11">
         <v>185.1</v>
@@ -3643,10 +3661,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C47" s="11">
         <v>187.4</v>
@@ -3660,10 +3678,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C48" s="11">
         <v>190.8</v>
@@ -3677,10 +3695,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C49" s="11">
         <v>192.4</v>
@@ -3694,10 +3712,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C50" s="11">
         <v>191.5</v>
@@ -3711,10 +3729,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C51" s="11">
         <v>190.3</v>
@@ -3728,10 +3746,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C52" s="11">
         <v>189.5</v>
@@ -3745,10 +3763,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C53" s="11">
         <v>189.7</v>
@@ -3762,10 +3780,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C54" s="11">
         <v>190.9</v>
@@ -3779,10 +3797,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C55" s="11">
         <v>191.1</v>
@@ -3796,10 +3814,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C56" s="11">
         <v>190.1</v>
@@ -3813,10 +3831,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C57" s="11">
         <v>191.6</v>
@@ -3830,10 +3848,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C58" s="11">
         <v>193.5</v>
@@ -3847,10 +3865,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C59" s="11">
         <v>193.4</v>
@@ -3864,10 +3882,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C60" s="11">
         <v>190.1</v>
@@ -3881,10 +3899,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C61" s="11">
         <v>188.1</v>
@@ -3898,10 +3916,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C62" s="11">
         <v>191</v>
@@ -3915,10 +3933,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C63" s="11">
         <v>198.3</v>
@@ -3932,10 +3950,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C64" s="11">
         <v>204.4</v>
@@ -3949,10 +3967,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="C65" s="11">
         <v>204.4</v>
@@ -3966,10 +3984,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C66" s="11">
         <v>204.3</v>
@@ -3983,10 +4001,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="C67" s="11">
         <v>204.6</v>
@@ -4000,10 +4018,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C68" s="11">
         <v>203.3</v>
@@ -4017,10 +4035,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C69" s="11">
         <v>201.7</v>
@@ -4034,10 +4052,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C70" s="11">
         <v>203</v>
@@ -4051,10 +4069,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C71" s="11">
         <v>202.4</v>
@@ -4068,10 +4086,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C72" s="11">
         <v>200.1</v>
@@ -4085,10 +4103,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C73" s="11">
         <v>202.7</v>
@@ -4102,10 +4120,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C74" s="11">
         <v>206.1</v>
@@ -4119,10 +4137,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="C75" s="11">
         <v>204</v>
@@ -4136,10 +4154,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C76" s="11">
         <v>204.2</v>
@@ -4153,10 +4171,10 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C77" s="11">
         <v>205.6</v>
@@ -4170,10 +4188,10 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C78" s="11">
         <v>200.5</v>
@@ -4187,10 +4205,10 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C79" s="11">
         <v>195.8</v>
@@ -4204,10 +4222,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C80" s="11">
         <v>193.8</v>
@@ -4221,10 +4239,10 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C81" s="11">
         <v>194.2</v>
@@ -4238,10 +4256,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C82" s="11">
         <v>197.3</v>
@@ -4255,10 +4273,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C83" s="11">
         <v>197.9</v>
@@ -4272,10 +4290,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C84" s="11">
         <v>195.2</v>
@@ -4289,10 +4307,10 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C85" s="11">
         <v>194.1</v>
@@ -4306,10 +4324,10 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C86" s="11">
         <v>192.6</v>
@@ -4323,10 +4341,10 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C87" s="11">
         <v>191.2</v>
@@ -4340,10 +4358,10 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C88" s="11">
         <v>192.1</v>
@@ -4357,10 +4375,10 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C89" s="11">
         <v>188.8</v>
@@ -4374,10 +4392,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C90" s="11">
         <v>188</v>
@@ -4391,10 +4409,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="C91" s="11">
         <v>188.6</v>
@@ -4408,10 +4426,10 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C92" s="11">
         <v>188.4</v>
@@ -4425,10 +4443,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C93" s="11">
         <v>187.2</v>
@@ -4442,10 +4460,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="C94" s="11">
         <v>185.6</v>
@@ -4459,10 +4477,10 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C95" s="11">
         <v>185.7</v>
@@ -4476,10 +4494,10 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C96" s="11">
         <v>185.7</v>
@@ -4493,10 +4511,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="C97" s="11">
         <v>186</v>
@@ -4510,10 +4528,10 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="C98" s="11">
         <v>187.2</v>
@@ -4527,10 +4545,10 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C99" s="11">
         <v>187.3</v>
@@ -4544,10 +4562,10 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C100" s="11">
         <v>185.6</v>
@@ -4561,10 +4579,10 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="C101" s="11">
         <v>184.5</v>
@@ -4578,10 +4596,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="C102" s="11">
         <v>188.3</v>
@@ -4595,10 +4613,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="C103" s="11">
         <v>194.1</v>
@@ -4612,10 +4630,10 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="C104" s="11">
         <v>196.6</v>
@@ -4629,10 +4647,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="C105" s="11">
         <v>197.6</v>
@@ -4646,10 +4664,10 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C106" s="11">
         <v>199.8</v>
@@ -4663,10 +4681,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="C107" s="11">
         <v>201.6</v>
@@ -4680,10 +4698,10 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C108" s="11">
         <v>198.8</v>
@@ -4697,10 +4715,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="C109" s="11">
         <v>196.4</v>
@@ -4714,10 +4732,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="C110" s="11">
         <v>196.6</v>
@@ -4731,10 +4749,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="C111" s="11">
         <v>196.3</v>
@@ -4748,10 +4766,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="C112" s="11">
         <v>194.6</v>
@@ -4765,10 +4783,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C113" s="11">
         <v>192.7</v>
@@ -4782,10 +4800,10 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="C114" s="11">
         <v>193</v>
@@ -4799,10 +4817,10 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="C115" s="11">
         <v>193.6</v>
@@ -4816,10 +4834,10 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C116" s="11">
         <v>192.7</v>
@@ -4833,10 +4851,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C117" s="11">
         <v>188.2</v>
@@ -4850,10 +4868,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C118" s="11">
         <v>184.8</v>
@@ -4867,10 +4885,10 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C119" s="11">
         <v>183.8</v>
@@ -4884,10 +4902,10 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C120" s="11">
         <v>181.8</v>
@@ -4901,10 +4919,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C121" s="11">
         <v>183.4</v>
@@ -4918,10 +4936,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C122" s="11">
         <v>185.9</v>
@@ -4935,10 +4953,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="C123" s="11">
         <v>183.7</v>
@@ -4952,10 +4970,10 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="C124" s="11">
         <v>182.8</v>
@@ -4969,10 +4987,10 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C125" s="11">
         <v>182.6</v>
@@ -4986,10 +5004,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C126" s="11">
         <v>181.2</v>
@@ -5003,10 +5021,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C127" s="11">
         <v>182</v>
@@ -5020,10 +5038,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C128" s="11">
         <v>183.7</v>
@@ -5037,10 +5055,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C129" s="11">
         <v>184.9</v>
@@ -5054,10 +5072,10 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C130" s="11">
         <v>186.6</v>
@@ -5071,10 +5089,10 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C131" s="11">
         <v>187.6</v>
@@ -5088,10 +5106,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="C132" s="11">
         <v>186.6</v>
@@ -5105,10 +5123,10 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="C133" s="11">
         <v>187.2</v>
@@ -5122,10 +5140,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C134" s="11">
         <v>185.7</v>
@@ -5139,10 +5157,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C135" s="11">
         <v>182.4</v>
@@ -5156,10 +5174,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C136" s="11">
         <v>182</v>
@@ -5173,10 +5191,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C137" s="11">
         <v>180.4</v>
@@ -5190,10 +5208,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C138" s="11">
         <v>178.8</v>
@@ -5207,10 +5225,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="C139" s="11">
         <v>178.6</v>
@@ -5224,10 +5242,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C140" s="11">
         <v>179.5</v>
@@ -5241,10 +5259,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="C141" s="11">
         <v>182.2</v>
@@ -5258,10 +5276,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="C142" s="11">
         <v>182.5</v>
@@ -5275,10 +5293,10 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C143" s="11">
         <v>183.1</v>
@@ -5292,10 +5310,10 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="C144" s="11">
         <v>185.6</v>
@@ -5309,10 +5327,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="C145" s="11">
         <v>185.7</v>
@@ -5326,10 +5344,10 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C146" s="11">
         <v>185.4</v>
@@ -5343,10 +5361,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="C147" s="11">
         <v>187.1</v>
@@ -5360,10 +5378,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="C148" s="11">
         <v>189</v>
@@ -5377,10 +5395,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C149" s="11">
         <v>187.3</v>
@@ -5394,10 +5412,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C150" s="11">
         <v>186.7</v>
@@ -5411,10 +5429,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="C151" s="11">
         <v>188.2</v>
@@ -5428,10 +5446,10 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="C152" s="11">
         <v>189.2</v>
@@ -5445,10 +5463,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="C153" s="11">
         <v>190.1</v>
@@ -5462,10 +5480,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="C154" s="11">
         <v>187.2</v>
@@ -5479,10 +5497,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C155" s="11">
         <v>185.4</v>
@@ -5496,10 +5514,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="C156" s="11">
         <v>185.4</v>
@@ -5513,10 +5531,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="C157" s="11">
         <v>186.2</v>
@@ -5530,10 +5548,10 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="C158" s="11">
         <v>186.5</v>
@@ -5547,10 +5565,10 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
       <c r="C159" s="11">
         <v>183.4</v>
@@ -5564,10 +5582,10 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="C160" s="11">
         <v>182.4</v>
@@ -5581,10 +5599,10 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="C161" s="11">
         <v>180.2</v>
@@ -5598,10 +5616,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="C162" s="11">
         <v>178.6</v>
@@ -5615,10 +5633,10 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="C163" s="11">
         <v>179.7</v>
@@ -5632,10 +5650,10 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="C164" s="11">
         <v>179.7</v>
@@ -5649,10 +5667,10 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="C165" s="11">
         <v>178.5</v>
@@ -5666,10 +5684,10 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="C166" s="11">
         <v>177.3</v>
@@ -5683,10 +5701,10 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="C167" s="11">
         <v>180.1</v>
@@ -5700,10 +5718,10 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" s="5" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="C168" s="11">
         <v>184.5</v>
@@ -5717,10 +5735,10 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" s="5" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="C169" s="11">
         <v>187.4</v>
@@ -5734,10 +5752,10 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A170" s="5" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="C170" s="11">
         <v>186.3</v>
@@ -5751,10 +5769,10 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A171" s="5" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="C171" s="11">
         <v>184.1</v>
@@ -5768,10 +5786,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A172" s="5" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="C172" s="11">
         <v>183.1</v>
@@ -5785,10 +5803,10 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" s="5" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="C173" s="11">
         <v>183.3</v>
@@ -5802,10 +5820,10 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" s="5" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="C174" s="11">
         <v>184.3</v>
@@ -5819,10 +5837,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" s="5" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="C175" s="11">
         <v>185.3</v>
@@ -5836,10 +5854,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" s="5" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="C176" s="11">
         <v>187.6</v>
@@ -5853,10 +5871,10 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="5" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="C177" s="11">
         <v>189.6</v>
@@ -5870,10 +5888,10 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="5" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="C178" s="11">
         <v>190</v>
@@ -5887,10 +5905,10 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="C179" s="11">
         <v>191.4</v>
@@ -5904,10 +5922,10 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="C180" s="11">
         <v>195.5</v>
@@ -5921,10 +5939,10 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
       <c r="C181" s="11">
         <v>199.3</v>
@@ -5938,10 +5956,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="5" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>762</v>
+        <v>768</v>
       </c>
       <c r="C182" s="11">
         <v>201.7</v>
@@ -5955,10 +5973,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="C183" s="11">
         <v>203.6</v>
@@ -5972,10 +5990,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="5" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>766</v>
+        <v>772</v>
       </c>
       <c r="C184" s="11">
         <v>203.4</v>
@@ -5989,10 +6007,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="C185" s="11">
         <v>202.8</v>
@@ -6006,10 +6024,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="5" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
       <c r="C186" s="11">
         <v>203.8</v>
@@ -6023,10 +6041,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="5" t="s">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="C187" s="11">
         <v>204.3</v>
@@ -6040,10 +6058,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="5" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
       <c r="C188" s="11">
         <v>207.1</v>
@@ -6057,10 +6075,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="C189" s="11">
         <v>209.9</v>
@@ -6074,10 +6092,10 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="5" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="C190" s="11">
         <v>212.5</v>
@@ -6091,10 +6109,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
-        <v>779</v>
+        <v>785</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="C191" s="11">
         <v>215.5</v>
@@ -6108,10 +6126,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="5" t="s">
-        <v>781</v>
+        <v>787</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="C192" s="11">
         <v>220.6</v>
@@ -6125,10 +6143,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="5" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>784</v>
+        <v>790</v>
       </c>
       <c r="C193" s="11">
         <v>225.3</v>
@@ -6142,10 +6160,10 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="5" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>786</v>
+        <v>792</v>
       </c>
       <c r="C194" s="11">
         <v>228.1</v>
@@ -6159,10 +6177,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="5" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="C195" s="11">
         <v>231.9</v>
@@ -6176,10 +6194,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="5" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="C196" s="11">
         <v>237.1</v>
@@ -6193,10 +6211,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="5" t="s">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="C197" s="11">
         <v>239.7</v>
@@ -6210,10 +6228,10 @@
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="5" t="s">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C198" s="11">
         <v>244.3</v>
@@ -6237,7 +6255,7 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="15" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
@@ -6246,7 +6264,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="15" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B202" s="15"/>
       <c r="C202" s="15"/>
@@ -6255,7 +6273,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" s="15" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
@@ -6264,7 +6282,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" s="15" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="B204" s="15"/>
       <c r="C204" s="15"/>
@@ -6273,7 +6291,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" s="15" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
@@ -6282,7 +6300,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="15" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -6291,7 +6309,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="15" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -6300,7 +6318,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="15" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -6309,7 +6327,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="15" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -6318,7 +6336,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="15" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
@@ -6327,7 +6345,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="15" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
@@ -6359,7 +6377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E214"/>
+  <dimension ref="A1:E217"/>
   <sheetFormatPr defaultColWidth="4.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.85546875" style="7" customWidth="1"/>
@@ -6380,7 +6398,7 @@
     </row>
     <row r="3" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -9670,13 +9688,13 @@
       <c r="B198" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="C198" s="12">
+      <c r="C198" s="11">
         <v>600.20000000000005</v>
       </c>
-      <c r="D198" s="14">
+      <c r="D198" s="13">
         <v>-0.1</v>
       </c>
-      <c r="E198" s="14">
+      <c r="E198" s="13">
         <v>-1</v>
       </c>
     </row>
@@ -9687,13 +9705,13 @@
       <c r="B199" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="C199" s="12">
+      <c r="C199" s="11">
         <v>599.6</v>
       </c>
-      <c r="D199" s="14">
+      <c r="D199" s="13">
         <v>-0.1</v>
       </c>
-      <c r="E199" s="14">
+      <c r="E199" s="13">
         <v>-1.7</v>
       </c>
     </row>
@@ -9704,56 +9722,80 @@
       <c r="B200" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="C200" s="12">
-        <v>601.4</v>
-      </c>
-      <c r="D200" s="14">
-        <v>0.3</v>
-      </c>
-      <c r="E200" s="14">
-        <v>-1.2</v>
+      <c r="C200" s="11">
+        <v>602</v>
+      </c>
+      <c r="D200" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="E200" s="13">
+        <v>-1.1000000000000001</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A201" s="4"/>
+      <c r="A201" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C201" s="12">
+        <v>599.6</v>
+      </c>
+      <c r="D201" s="14">
+        <v>-0.4</v>
+      </c>
+      <c r="E201" s="14">
+        <v>-1.3</v>
+      </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A202" s="6"/>
-      <c r="B202" s="10"/>
-      <c r="C202" s="10"/>
-      <c r="D202" s="10"/>
-      <c r="E202" s="10"/>
+      <c r="A202" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B202" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C202" s="12">
+        <v>593</v>
+      </c>
+      <c r="D202" s="14">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="E202" s="14">
+        <v>-2</v>
+      </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A203" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="B203" s="15"/>
-      <c r="C203" s="15"/>
-      <c r="D203" s="15"/>
-      <c r="E203" s="15"/>
+      <c r="A203" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="C203" s="12">
+        <v>593.6</v>
+      </c>
+      <c r="D203" s="14">
+        <v>0.1</v>
+      </c>
+      <c r="E203" s="14">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A204" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="B204" s="15"/>
-      <c r="C204" s="15"/>
-      <c r="D204" s="15"/>
-      <c r="E204" s="15"/>
+      <c r="A204" s="4"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A205" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="B205" s="15"/>
-      <c r="C205" s="15"/>
-      <c r="D205" s="15"/>
-      <c r="E205" s="15"/>
+      <c r="A205" s="6"/>
+      <c r="B205" s="10"/>
+      <c r="C205" s="10"/>
+      <c r="D205" s="10"/>
+      <c r="E205" s="10"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" s="15" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B206" s="15"/>
       <c r="C206" s="15"/>
@@ -9762,7 +9804,7 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" s="15" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
@@ -9771,7 +9813,7 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" s="15" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B208" s="15"/>
       <c r="C208" s="15"/>
@@ -9780,7 +9822,7 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" s="15" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
@@ -9789,7 +9831,7 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" s="15" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B210" s="15"/>
       <c r="C210" s="15"/>
@@ -9798,7 +9840,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" s="15" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
@@ -9807,7 +9849,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" s="15" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B212" s="15"/>
       <c r="C212" s="15"/>
@@ -9816,7 +9858,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" s="15" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
@@ -9825,30 +9867,57 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" s="15" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B214" s="15"/>
       <c r="C214" s="15"/>
       <c r="D214" s="15"/>
       <c r="E214" s="15"/>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A215" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="B215" s="15"/>
+      <c r="C215" s="15"/>
+      <c r="D215" s="15"/>
+      <c r="E215" s="15"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A216" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="B216" s="15"/>
+      <c r="C216" s="15"/>
+      <c r="D216" s="15"/>
+      <c r="E216" s="15"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A217" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="B217" s="15"/>
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A203:E203"/>
-    <mergeCell ref="A204:E204"/>
+    <mergeCell ref="A206:E206"/>
+    <mergeCell ref="A207:E207"/>
+    <mergeCell ref="A213:E213"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A216:E216"/>
+    <mergeCell ref="A217:E217"/>
+    <mergeCell ref="A208:E208"/>
+    <mergeCell ref="A209:E209"/>
     <mergeCell ref="A210:E210"/>
     <mergeCell ref="A211:E211"/>
     <mergeCell ref="A212:E212"/>
-    <mergeCell ref="A213:E213"/>
-    <mergeCell ref="A214:E214"/>
-    <mergeCell ref="A205:E205"/>
-    <mergeCell ref="A206:E206"/>
-    <mergeCell ref="A207:E207"/>
-    <mergeCell ref="A208:E208"/>
-    <mergeCell ref="A209:E209"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.5"/>
